--- a/data/wrong_words.xlsx
+++ b/data/wrong_words.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>word</t>
   </si>
   <si>
-    <t>a</t>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -45,7 +45,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -64,12 +64,6 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Times Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -424,7 +418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -449,31 +443,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -486,21 +465,6 @@
       </right>
       <top style="thin">
         <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
       </top>
       <bottom style="thin">
         <color indexed="9"/>
@@ -625,152 +589,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -780,22 +744,16 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1973,283 +1931,163 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1" spans="1:7">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
     </row>
     <row r="6" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
     </row>
     <row r="7" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
     </row>
     <row r="8" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
     </row>
     <row r="9" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" ht="20.05" customHeight="1" spans="1:7">
-      <c r="A13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+    </row>
+    <row r="10" ht="20.05" customHeight="1" spans="4:7">
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11" ht="20.05" customHeight="1" spans="4:7">
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12" ht="20.05" customHeight="1" spans="4:7">
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+    <row r="13" ht="20.05" customHeight="1" spans="4:7">
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+    </row>
+    <row r="14" ht="20.05" customHeight="1" spans="4:8">
       <c r="D14"/>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
       <c r="H14"/>
     </row>
-    <row r="15" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
+    <row r="15" ht="20.05" customHeight="1" spans="4:8">
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
       <c r="H15"/>
     </row>
-    <row r="16" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
+    <row r="16" ht="20.05" customHeight="1" spans="4:8">
       <c r="D16"/>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16"/>
     </row>
-    <row r="17" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
+    <row r="17" ht="20.05" customHeight="1" spans="8:8">
       <c r="H17"/>
     </row>
-    <row r="18" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
+    <row r="18" ht="20.05" customHeight="1" spans="8:8">
       <c r="H18"/>
     </row>
-    <row r="19" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
+    <row r="19" ht="20.05" customHeight="1" spans="8:8">
       <c r="H19"/>
     </row>
-    <row r="20" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
+    <row r="20" ht="20.05" customHeight="1" spans="8:8">
       <c r="H20"/>
     </row>
-    <row r="21" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
+    <row r="21" ht="20.05" customHeight="1" spans="8:8">
       <c r="H21"/>
     </row>
-    <row r="22" ht="20.05" customHeight="1" spans="1:8">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
+    <row r="22" ht="20.05" customHeight="1" spans="8:8">
       <c r="H22"/>
     </row>
-    <row r="23" customHeight="1" spans="1:8">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
+    <row r="23" customHeight="1" spans="8:8">
       <c r="H23"/>
     </row>
-    <row r="24" customHeight="1" spans="1:8">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
+    <row r="24" customHeight="1" spans="8:8">
       <c r="H24"/>
     </row>
-    <row r="25" customHeight="1" spans="1:8">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
+    <row r="25" customHeight="1" spans="8:8">
       <c r="H25"/>
     </row>
-    <row r="26" customHeight="1" spans="1:8">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
+    <row r="26" customHeight="1" spans="8:8">
       <c r="H26"/>
     </row>
-    <row r="27" customHeight="1" spans="1:8">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
+    <row r="27" customHeight="1" spans="8:8">
       <c r="H27"/>
     </row>
   </sheetData>
